--- a/HL7-AT-FHIR-Core-R5/all-profiles.xlsx
+++ b/HL7-AT-FHIR-Core-R5/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T14:21:13+00:00</t>
+    <t>2025-01-27T06:12:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HL7-AT-FHIR-Core-R5/all-profiles.xlsx
+++ b/HL7-AT-FHIR-Core-R5/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T06:12:08+00:00</t>
+    <t>2025-01-24T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
